--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-autorisation-substitution.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-autorisation-substitution.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="252">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,123 +520,105 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis</t>
   </si>
   <si>
-    <t>Act.text</t>
+    <t>Act.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Act.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Act.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Act.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Act.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Act.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
 </t>
   </si>
   <si>
-    <t>Act.statusCode</t>
-  </si>
-  <si>
-    <t>Statut de l’entrée. Fixé à la valeur 'completed'</t>
-  </si>
-  <si>
-    <t>Statut de l’entrée</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActStatus</t>
-  </si>
-  <si>
-    <t>Act.statusCode.nullFlavor</t>
-  </si>
-  <si>
-    <t>Act.statusCode.code</t>
-  </si>
-  <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
-    <t>completed</t>
-  </si>
-  <si>
-    <t>CD.code</t>
-  </si>
-  <si>
-    <t>Act.statusCode.codeSystem</t>
-  </si>
-  <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
-    <t>Act.statusCode.codeSystemName</t>
-  </si>
-  <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
-    <t>Act.statusCode.codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Act.statusCode.displayName</t>
-  </si>
-  <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
-    <t>Act.statusCode.sdtcValueSet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
-    <t>Act.statusCode.sdtcValueSetVersion</t>
-  </si>
-  <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
-    <t>Act.statusCode.originalText</t>
-  </si>
-  <si>
-    <t>Original Text</t>
-  </si>
-  <si>
     <t>The text or phrase used as the basis for the coding.</t>
   </si>
   <si>
     <t>CD.originalText</t>
   </si>
   <si>
-    <t>Act.statusCode.qualifier</t>
+    <t>Act.code.qualifier</t>
   </si>
   <si>
     <t>Qualifier</t>
@@ -652,16 +634,67 @@
     <t>CD.qualifier</t>
   </si>
   <si>
+    <t>Act.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
+    <t>Act.text</t>
+  </si>
+  <si>
+    <t>Act.statusCode</t>
+  </si>
+  <si>
+    <t>Statut de l’entrée. Fixé à la valeur 'completed'</t>
+  </si>
+  <si>
+    <t>Statut de l’entrée</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActStatus</t>
+  </si>
+  <si>
+    <t>Act.statusCode.nullFlavor</t>
+  </si>
+  <si>
+    <t>Act.statusCode.code</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>Act.statusCode.codeSystem</t>
+  </si>
+  <si>
+    <t>Act.statusCode.codeSystemName</t>
+  </si>
+  <si>
+    <t>Act.statusCode.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Act.statusCode.displayName</t>
+  </si>
+  <si>
+    <t>Act.statusCode.sdtcValueSet</t>
+  </si>
+  <si>
+    <t>Act.statusCode.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Act.statusCode.originalText</t>
+  </si>
+  <si>
+    <t>Act.statusCode.qualifier</t>
+  </si>
+  <si>
     <t>Act.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>
@@ -1081,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:AK66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.35546875" customWidth="true" bestFit="true"/>
@@ -3993,7 +4026,9 @@
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E29" s="2"/>
+      <c r="E29" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4010,10 +4045,12 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
+      <c r="M29" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4039,13 +4076,11 @@
         <v>74</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>74</v>
@@ -4063,7 +4098,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4083,16 +4118,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F30" t="s" s="2">
         <v>75</v>
       </c>
@@ -4109,13 +4146,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4142,11 +4177,13 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4164,7 +4201,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4182,28 +4219,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4212,11 +4249,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4243,11 +4280,13 @@
         <v>74</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4265,7 +4304,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4285,17 +4324,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4313,11 +4352,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4329,7 +4368,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4368,7 +4407,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4388,23 +4427,23 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>74</v>
@@ -4416,11 +4455,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4471,7 +4510,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4489,28 +4528,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4523,7 +4562,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4574,7 +4613,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4594,23 +4633,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E35" t="s" s="2">
-        <v>184</v>
-      </c>
+      <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -4622,11 +4659,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4677,7 +4714,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4697,23 +4734,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>188</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -4809,7 +4844,9 @@
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
@@ -4826,11 +4863,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4881,7 +4918,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4901,21 +4938,23 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
@@ -4927,11 +4966,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4982,13 +5021,13 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
@@ -5002,23 +5041,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5030,11 +5069,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5085,13 +5124,13 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
@@ -5105,23 +5144,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E40" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5133,12 +5170,10 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="L40" s="2"/>
-      <c r="M40" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5188,59 +5223,59 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="F41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5267,13 +5302,11 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -5291,13 +5324,13 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>74</v>
@@ -5311,16 +5344,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5337,10 +5372,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>212</v>
+        <v>85</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5366,13 +5403,11 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5390,7 +5425,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>211</v>
+        <v>89</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5410,16 +5445,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -5436,10 +5473,12 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
+      <c r="M43" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5450,7 +5489,7 @@
         <v>74</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>74</v>
@@ -5465,11 +5504,13 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>216</v>
+        <v>74</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5487,7 +5528,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5507,21 +5548,23 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>74</v>
@@ -5533,10 +5576,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5562,11 +5607,13 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>218</v>
+        <v>74</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -5584,7 +5631,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5604,21 +5651,23 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5630,10 +5679,12 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
+      <c r="M45" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5683,7 +5734,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5703,21 +5754,23 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" s="2"/>
+      <c r="E46" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>74</v>
@@ -5729,10 +5782,12 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
+      <c r="M46" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5782,13 +5837,13 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>74</v>
@@ -5802,21 +5857,23 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" s="2"/>
+      <c r="E47" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -5828,10 +5885,12 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>224</v>
+        <v>102</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
+      <c r="M47" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -5881,13 +5940,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -5901,10 +5960,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5915,7 +5974,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -5927,10 +5986,12 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -5980,13 +6041,13 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>74</v>
@@ -6000,10 +6061,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6014,7 +6075,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -6026,10 +6087,12 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
+      <c r="M49" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6079,13 +6142,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>74</v>
@@ -6099,21 +6162,23 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6125,10 +6190,12 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6178,13 +6245,13 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>74</v>
@@ -6198,21 +6265,23 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6224,10 +6293,12 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
+      <c r="M51" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6277,7 +6348,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6297,21 +6368,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6323,10 +6396,12 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
+      <c r="M52" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6376,7 +6451,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6396,10 +6471,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6410,7 +6485,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -6422,7 +6497,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6475,13 +6550,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6495,10 +6570,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6509,7 +6584,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -6521,7 +6596,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6550,13 +6625,11 @@
         <v>74</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -6574,13 +6647,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -6594,10 +6667,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6608,7 +6681,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -6620,7 +6693,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>240</v>
+        <v>91</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6649,13 +6722,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>229</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -6673,26 +6744,1115 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K60" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK55" t="s" s="2">
+      <c r="AI60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK66" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK55">
+  <autoFilter ref="A1:AK66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6702,7 +7862,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI54">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-autorisation-substitution.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-autorisation-substitution.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
